--- a/all-sectors-meta-updated-050126.xlsx
+++ b/all-sectors-meta-updated-050126.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rooted-attalla/Documents/Rooted/rooted-website-overhaul/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rooted-attalla/Documents/Rooted/rooted-website-content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A96CA3B-92DB-3145-A7CA-E205A2AFB585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA0CA04-4F70-BA4C-8002-A363664C3D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38460" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{31247973-208E-7D4B-B607-1EC6C109F610}"/>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{31247973-208E-7D4B-B607-1EC6C109F610}"/>
   </bookViews>
   <sheets>
     <sheet name="Sectors Meta" sheetId="4" r:id="rId1"/>
@@ -46,13 +46,7 @@
     <t>Industries</t>
   </si>
   <si>
-    <t>Short Descriptions (Med., ~110-125 characters)</t>
-  </si>
-  <si>
     <t>On-Page Description (Med-Long., ~40-60 words)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta Descriptions (Short, ~60 characters) </t>
   </si>
   <si>
     <t>Logistics &amp; Transportation</t>
@@ -1105,6 +1099,12 @@
   <si>
     <t>Build Workforce Resilience
  Sustainable 3PL performance demands workforce capability. We analyze turnover root causes (compensation, work conditions, management, career development) and design retention strategies: competitive pay, flexible scheduling, clear career paths, performance recognition, and frontline leadership development. We design organizational structures for client growth, including account management, operations capacity, and coordination. We develop workforce planning models considering seasonality, client acquisition, and automation.</t>
+  </si>
+  <si>
+    <t>Meta Descriptions (Med., ~110-125 characters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page/Sector Excerpts (Short, ~60 characters) </t>
   </si>
 </sst>
 </file>
@@ -1738,19 +1738,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="6" t="s">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" s="10" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -1758,78 +1758,82 @@
     </row>
     <row r="3" spans="1:5" ht="86" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>8</v>
-      </c>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="52" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>12</v>
-      </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="D5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" ht="86" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="B7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" spans="1:5" ht="69" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="C7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>24</v>
-      </c>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" s="10" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1837,105 +1841,107 @@
     </row>
     <row r="9" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>29</v>
-      </c>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="D14" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="69" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="15" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1943,77 +1949,77 @@
     </row>
     <row r="17" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="D17" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="D18" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="D20" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="D21" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="15" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2021,161 +2027,161 @@
     </row>
     <row r="23" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="D23" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>85</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="D26" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="D27" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="D28" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="D29" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="D30" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="D31" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="35" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="D32" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="D33" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="18" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="17"/>
@@ -2183,77 +2189,77 @@
     </row>
     <row r="35" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="D36" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="D37" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="D38" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="D39" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="18" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="17"/>
@@ -2261,86 +2267,86 @@
     </row>
     <row r="41" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="D41" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="D42" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="D43" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="D44" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="52" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="D45" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="D46" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -2380,108 +2386,108 @@
     <row r="1" spans="1:7" s="2" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="70" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="408" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="235" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="235" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2503,84 +2509,84 @@
   <sheetData>
     <row r="1" spans="1:2" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B6" s="23"/>
     </row>
     <row r="7" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B8" s="23"/>
     </row>
     <row r="9" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B10" s="23"/>
     </row>
     <row r="11" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B11" s="23"/>
     </row>
     <row r="12" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B12" s="23"/>
     </row>
     <row r="13" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B13" s="23"/>
     </row>
     <row r="14" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B14" s="23"/>
     </row>
@@ -2589,172 +2595,172 @@
     </row>
     <row r="16" spans="1:2" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A44" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" s="23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="23" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A51" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A52" s="23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -2776,12 +2782,12 @@
   <sheetData>
     <row r="1" spans="1:3" s="24" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B2" s="23"/>
     </row>
@@ -2826,42 +2832,42 @@
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C31"/>
     </row>
     <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C40"/>
     </row>
     <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C46"/>
     </row>
     <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="24" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C50"/>
     </row>
@@ -3030,273 +3036,273 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>191</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="30" t="s">
         <v>194</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="32" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="120" x14ac:dyDescent="0.2">
+      <c r="A5" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="C5" s="30" t="s">
         <v>200</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="32" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="71" x14ac:dyDescent="0.2">
+      <c r="A7" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="B7" s="32" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="43" x14ac:dyDescent="0.2">
-      <c r="A7" s="30" t="s">
+      <c r="C7" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="32" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="71" x14ac:dyDescent="0.2">
+      <c r="A8" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="B8" s="32" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="43" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
+      <c r="C8" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="32" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A9" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
+      <c r="C9" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="31" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="71" x14ac:dyDescent="0.2">
+      <c r="A10" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="B10" s="32" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="43" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
+      <c r="C10" s="30" t="s">
         <v>215</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A11" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>218</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>221</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>224</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>227</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>230</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>233</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A17" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>236</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>239</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>242</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>245</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B21" s="33"/>
       <c r="C21" s="33"/>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>249</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>252</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>255</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="C25" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="31" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A26" s="30" t="s">
         <v>259</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="30" t="s">
+      <c r="C26" s="30" t="s">
         <v>261</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3325,200 +3331,200 @@
   <sheetData>
     <row r="1" spans="1:32" ht="14" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>320</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="E1" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="G1" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q1" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="S1" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="T1" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="U1" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="V1" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="W1" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="X1" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y1" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z1" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA1" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB1" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="AC1" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD1" s="25" t="s">
         <v>323</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="O1" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="P1" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q1" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="R1" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="S1" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="T1" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="U1" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="V1" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="W1" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="X1" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y1" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="Z1" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA1" s="25" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB1" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="AC1" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="AD1" s="25" t="s">
-        <v>325</v>
       </c>
       <c r="AE1" s="25"/>
       <c r="AF1" s="25"/>
     </row>
     <row r="2" spans="1:32" ht="261" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="F2" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="G2" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>330</v>
-      </c>
       <c r="H2" s="25" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P2" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="S2" s="29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T2" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U2" s="29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V2" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W2" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X2" s="25"/>
       <c r="Y2" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z2" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA2" s="25" t="s">
         <v>331</v>
-      </c>
-      <c r="Z2" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA2" s="25" t="s">
-        <v>333</v>
       </c>
       <c r="AB2" s="25"/>
       <c r="AC2" s="29" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AD2" s="25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AE2" s="25"/>
       <c r="AF2" s="25"/>
     </row>
     <row r="3" spans="1:32" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="25" t="s">
         <v>335</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>337</v>
       </c>
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
@@ -3551,16 +3557,16 @@
     </row>
     <row r="4" spans="1:32" ht="27" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
@@ -3593,16 +3599,16 @@
     </row>
     <row r="5" spans="1:32" ht="27" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
@@ -3635,16 +3641,16 @@
     </row>
     <row r="6" spans="1:32" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
@@ -3677,16 +3683,16 @@
     </row>
     <row r="7" spans="1:32" ht="27" x14ac:dyDescent="0.2">
       <c r="A7" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>341</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>342</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>343</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
@@ -3794,6 +3800,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100918E1626A5BB1D40B2702FB97BC40A9D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4a01d9c5056f75993012e94a2c391c63">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48fa0c3f-97ce-49b9-83dd-86daf558ed18" xmlns:ns3="0e6bc162-9f94-4e5b-81f6-daa1750a7489" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="784eabd0e8225fe43d48563102b940d3" ns2:_="" ns3:_="">
     <xsd:import namespace="48fa0c3f-97ce-49b9-83dd-86daf558ed18"/>
@@ -4036,15 +4051,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4058,6 +4064,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95B7348-0055-4611-847C-7A219C8A2C41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6646D813-A75C-48E1-9F85-CDAF1ECC5AB5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4072,14 +4086,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95B7348-0055-4611-847C-7A219C8A2C41}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
